--- a/backend/excel/Conveyor Calculation Official.xlsx
+++ b/backend/excel/Conveyor Calculation Official.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BIT\Desktop\SAIL\mechanical-calculator\backend\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E47A3E84-7E57-4212-A9C1-C76A8C0F6672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AFB8C3-8E38-4933-B1F5-9DBB0A3B7919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="845" activeTab="3" xr2:uid="{32EF1FDB-14A2-4648-B3FE-9BD34F418C5F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="845" firstSheet="3" activeTab="3" xr2:uid="{32EF1FDB-14A2-4648-B3FE-9BD34F418C5F}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT SHEET" sheetId="10" r:id="rId1"/>
@@ -4873,17 +4873,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4908,7 +4908,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="9" dropStyle="combo" dx="31" fmlaLink="B20" fmlaRange="'DATA BANK'!$A$35:$A$39" noThreeD="1" sel="2" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="9" dropStyle="combo" dx="31" fmlaLink="B20" fmlaRange="'DATA BANK'!$A$35:$A$39" noThreeD="1" sel="3" val="0"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5740,10 +5740,10 @@
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
-      <c r="G5" s="229"/>
-      <c r="H5" s="229"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="232"/>
+      <c r="G5" s="230"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="229"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="231"/>
@@ -5777,20 +5777,20 @@
       </c>
       <c r="G6" s="153"/>
       <c r="H6" s="153"/>
-      <c r="I6" s="229"/>
-      <c r="J6" s="229"/>
+      <c r="I6" s="230"/>
+      <c r="J6" s="230"/>
       <c r="K6" s="153"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="229"/>
-      <c r="O6" s="229"/>
-      <c r="P6" s="229"/>
-      <c r="Q6" s="229"/>
-      <c r="R6" s="229"/>
-      <c r="S6" s="229"/>
-      <c r="T6" s="229"/>
-      <c r="U6" s="229"/>
-      <c r="V6" s="229"/>
+      <c r="N6" s="230"/>
+      <c r="O6" s="230"/>
+      <c r="P6" s="230"/>
+      <c r="Q6" s="230"/>
+      <c r="R6" s="230"/>
+      <c r="S6" s="230"/>
+      <c r="T6" s="230"/>
+      <c r="U6" s="230"/>
+      <c r="V6" s="230"/>
       <c r="W6" s="3"/>
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
@@ -5817,8 +5817,8 @@
         <f t="array" ref="H7:H10">_xlfn._xlws.FILTER($B$6:$B$26,$A$6:$A$26=POWER!B12)</f>
         <v>114.3</v>
       </c>
-      <c r="I7" s="232"/>
-      <c r="J7" s="232"/>
+      <c r="I7" s="229"/>
+      <c r="J7" s="229"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="153"/>
@@ -5854,8 +5854,8 @@
       <c r="H8" s="13">
         <v>127</v>
       </c>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
+      <c r="I8" s="230"/>
+      <c r="J8" s="230"/>
       <c r="K8" s="153"/>
       <c r="L8" s="3"/>
       <c r="M8" s="152"/>
@@ -5920,8 +5920,8 @@
       <c r="H10" s="13">
         <v>152.4</v>
       </c>
-      <c r="I10" s="230"/>
-      <c r="J10" s="230"/>
+      <c r="I10" s="232"/>
+      <c r="J10" s="232"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="152"/>
@@ -5955,8 +5955,8 @@
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="13"/>
-      <c r="I11" s="230"/>
-      <c r="J11" s="230"/>
+      <c r="I11" s="232"/>
+      <c r="J11" s="232"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="152"/>
@@ -5990,8 +5990,8 @@
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="13"/>
-      <c r="I12" s="229"/>
-      <c r="J12" s="229"/>
+      <c r="I12" s="230"/>
+      <c r="J12" s="230"/>
       <c r="K12" s="153"/>
       <c r="L12" s="3"/>
       <c r="M12" s="152"/>
@@ -6025,8 +6025,8 @@
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="13"/>
-      <c r="I13" s="229"/>
-      <c r="J13" s="229"/>
+      <c r="I13" s="230"/>
+      <c r="J13" s="230"/>
       <c r="K13" s="153"/>
       <c r="L13" s="3"/>
       <c r="M13" s="153"/>
@@ -6461,15 +6461,15 @@
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
-      <c r="N26" s="229"/>
-      <c r="O26" s="229"/>
-      <c r="P26" s="229"/>
-      <c r="Q26" s="229"/>
-      <c r="R26" s="229"/>
-      <c r="S26" s="229"/>
-      <c r="T26" s="229"/>
-      <c r="U26" s="229"/>
-      <c r="V26" s="229"/>
+      <c r="N26" s="230"/>
+      <c r="O26" s="230"/>
+      <c r="P26" s="230"/>
+      <c r="Q26" s="230"/>
+      <c r="R26" s="230"/>
+      <c r="S26" s="230"/>
+      <c r="T26" s="230"/>
+      <c r="U26" s="230"/>
+      <c r="V26" s="230"/>
       <c r="W26" s="3"/>
       <c r="X26" s="2"/>
       <c r="Y26" s="2"/>
@@ -8869,12 +8869,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="M5:V5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="N6:V6"/>
     <mergeCell ref="N26:V26"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
@@ -8882,6 +8876,12 @@
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="M25:V25"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="M5:V5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="N6:V6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9491,7 +9491,7 @@
         <v>160</v>
       </c>
       <c r="B20" s="88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" s="88" t="s">
         <v>112</v>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="B162" s="87">
         <f>INDEX('DATA BANK'!A35:C39,B20,3)</f>
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D162" s="88"/>
       <c r="E162" s="71"/>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="B163" s="133">
         <f>+(B160*100)/B162</f>
-        <v>89.09946747276355</v>
+        <v>80.189520725487199</v>
       </c>
       <c r="D163" s="88"/>
       <c r="E163" s="71"/>
